--- a/AAII_Financials/Quarterly/BNDSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNDSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="92">
   <si>
     <t>BNDSY</t>
   </si>
@@ -656,68 +656,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,8 +763,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -798,8 +810,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -839,8 +857,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -856,8 +880,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -897,8 +923,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -938,8 +970,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,8 +1017,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,8 +1064,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1034,8 +1084,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1075,8 +1127,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1116,8 +1174,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,8 +1197,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1174,8 +1240,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1215,8 +1287,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1256,8 +1334,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1297,8 +1381,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1338,8 +1428,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1379,8 +1475,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1420,8 +1522,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1461,8 +1569,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1502,8 +1616,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,8 +1663,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1584,8 +1710,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1625,8 +1757,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1666,8 +1804,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1707,8 +1851,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1748,8 +1898,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1789,54 +1945,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1852,8 +2020,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1869,377 +2039,433 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1640000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11005400</v>
+      </c>
+      <c r="F41" s="3">
         <v>1609900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1666400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>32543200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1321600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>33363800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1377600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>30521100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1568700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>37330700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1711200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>41387400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2162700</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22868800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5273800</v>
+      </c>
+      <c r="F42" s="3">
         <v>17320000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>18339100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>4379600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>17257800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>5408200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>4999000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>5185000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>11255100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>6102900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>6396200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>5774700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>5924700</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>503000</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>568900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>540600</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3">
         <v>564100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>7065600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>580800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>7006100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>499900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>7125300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>333500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>7396800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>220800</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>501800</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>540300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>497300</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3">
         <v>523000</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3">
         <v>497200</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
         <v>651600</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3">
         <v>619900</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>61027300</v>
+      </c>
+      <c r="F45" s="3">
         <v>61307300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>355200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>273500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>266800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1215700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>479900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1274100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>348900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1100800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>345900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1070200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>270100</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30117200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>77306600</v>
+      </c>
+      <c r="F46" s="3">
         <v>94299400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>50688100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>37196300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>37642800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>47053300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>38167300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>43986400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>45900000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>51659600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>41271300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>55629100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>51185700</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40819800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>40705600</v>
+      </c>
+      <c r="F47" s="3">
         <v>39405200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>40517100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>35160000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>33066400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>34311800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>31917200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>31608600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>31376300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>29160700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>30675600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>30847500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>29613600</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1767600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1968200</v>
+      </c>
+      <c r="F48" s="3">
         <v>1877300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2165500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2187600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2067400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2384600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2144600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2463000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2284900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2522200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2354400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2686900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2438900</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2748400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2858300</v>
+      </c>
+      <c r="F49" s="3">
         <v>2927500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3002200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2755100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2648300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2806200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2672000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2685300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2744600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2567700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2667700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2677100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2654900</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2279,8 +2505,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2320,49 +2552,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>473700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7470300</v>
+      </c>
+      <c r="F52" s="3">
         <v>481200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>715500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>9845400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>557200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>542000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>666700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>551300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>666900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>508000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>765500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>593200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>732700</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2402,49 +2646,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>227446500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>286974500</v>
+      </c>
+      <c r="F54" s="3">
         <v>288120700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>296386100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>269332000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>248056700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>273827800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>261789100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>254757800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>259945800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>257473500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>265778100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>269969600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>268506200</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2460,8 +2716,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2477,254 +2735,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>156285100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>173617000</v>
+      </c>
+      <c r="F57" s="3">
         <v>158819900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>201281400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>195813900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>179650000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>200393700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>181139700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>191975400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>190205700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>200082600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>190417400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>213842900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>208082400</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23879900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>11234900</v>
+      </c>
+      <c r="F58" s="3">
         <v>24209300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>33610800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>17808000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>15928300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>14352000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>28568300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>8361200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>17336100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>607500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>22091100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>968100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>13949600</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1078000</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>62407600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>642100</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
         <v>5040300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3237800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>789900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3696200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5622900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4462300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>719900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>4130800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>5014900</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>181648900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>185008600</v>
+      </c>
+      <c r="F60" s="3">
         <v>245865500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>236046700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>214114800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>201117300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>218492100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>210936600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>204419000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>213800300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>205376800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>213690900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>219000400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>227046900</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23149100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>23197300</v>
+      </c>
+      <c r="F61" s="3">
         <v>24081600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>32316000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>29509300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>29450000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>29998900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>26512000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>27567200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>28708200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>29055900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>26852900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>28116000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>25070200</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8546700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>62605800</v>
+      </c>
+      <c r="F62" s="3">
         <v>1439200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>10797700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>9794600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1744700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>9249400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>8736200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>7408600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1904500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>8457900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>10282100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>8571300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2214400</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2764,8 +3060,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2805,8 +3107,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2846,49 +3154,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>213537200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>270811700</v>
+      </c>
+      <c r="F66" s="3">
         <v>271587100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>279368300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>253418700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>232493400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>257740400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>246362300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>239394800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>244604600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>242890600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>251017700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>255687700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>254520800</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2904,8 +3224,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2945,8 +3267,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2986,8 +3314,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3027,8 +3361,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3068,49 +3408,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8568800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-407000</v>
+      </c>
+      <c r="F72" s="3">
         <v>10818800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>10656900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>528500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>9081100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>965900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>8729500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>8369500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>7587500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>7092900</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3150,8 +3502,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3191,8 +3549,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3232,49 +3596,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13866200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16120100</v>
+      </c>
+      <c r="F76" s="3">
         <v>16493000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>16976000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15876600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>15527600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16049500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>15389400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>15326400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>15303400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>14547000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>14722100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>14244900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13948700</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3314,54 +3690,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3401,8 +3789,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3418,8 +3812,10 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3459,8 +3855,14 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3500,8 +3902,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3541,8 +3949,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3582,8 +3996,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3623,8 +4043,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3664,8 +4090,14 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3705,8 +4137,14 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3722,8 +4160,10 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3763,8 +4203,14 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3804,8 +4250,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3845,8 +4297,14 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3886,8 +4344,14 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3903,8 +4367,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3944,8 +4410,14 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3985,8 +4457,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4026,8 +4504,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4067,8 +4551,14 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4108,8 +4598,14 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4149,8 +4645,14 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4188,6 +4690,12 @@
         <v>4</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
